--- a/documentacao/Testes/Caso de Teste/UC49 -  EXIBIR REPUTAÇÃO DA CLINICA.xlsx
+++ b/documentacao/Testes/Caso de Teste/UC49 -  EXIBIR REPUTAÇÃO DA CLINICA.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="83">
   <si>
     <t xml:space="preserve">ID Caso de Teste</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">Resultado Esperado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado Obtido</t>
   </si>
   <si>
     <t xml:space="preserve">Status (OK/NOK)</t>
@@ -531,7 +528,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
@@ -564,358 +561,421 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
